--- a/Result/profitability/4188.xlsx
+++ b/Result/profitability/4188.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7499,6 +7499,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-22</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-334.67%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-19</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="N58" t="n">
+        <v>40.81625</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-0.2452830188679246</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.559999999999995</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.04426787741203175</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
